--- a/data/trans_dic/IP16B98-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP16B98-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -513,7 +514,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero otros medicamentos recetados por el médico</t>
+          <t>Menores que consumiero otros medicamentos recetados por el médico (tasa de respuesta: 96,06%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -631,7 +632,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>51,01; 100,0</t>
+          <t>50,91; 100,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -641,7 +642,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>73,58; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -651,12 +652,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>72,48; 100,0</t>
+          <t>72,62; 100,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>41,08; 92,04</t>
+          <t>34,85; 92,05</t>
         </is>
       </c>
     </row>
@@ -711,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>36,85; 100,0</t>
+          <t>35,65; 100,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>84,31; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>56,72; 100,0</t>
+          <t>61,54; 100,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>82,92; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>68,65; 100,0</t>
+          <t>69,19; 100,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>91,36; 100</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -791,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>76,75; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>79,25; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>31,28; 100,0</t>
+          <t>30,07; 100,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>84,31; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>53,12; 100,0</t>
+          <t>57,36; 100,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>90,51; 100</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -871,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>55,59; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>73,58; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>79,25; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>79,25; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>84,31; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,39; 100</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -951,32 +952,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>74,62; 100,0</t>
+          <t>74,38; 100,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>88,2; 100,0</t>
+          <t>88,45; 100,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>75,22; 100,0</t>
+          <t>74,58; 100,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>80,44; 100,0</t>
+          <t>80,27; 100,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>82,25; 98,26</t>
+          <t>81,86; 97,25</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>87,49; 98,77</t>
+          <t>86,74; 98,77</t>
         </is>
       </c>
     </row>
@@ -1001,4 +1002,706 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que consumiero otros medicamentos recetados por el médico (tasa de respuesta: 96,06%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>4823</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>3774</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1192</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>9128</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>4966</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>2775; 5450</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1912; 4328</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2714</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>7084; 9755</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>2454; 6482</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>4036</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>7828</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>7055</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>7012</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>11091</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>14839</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>1646; 4618</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>4756; 7728</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>8543; 12346</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>4875</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>5587</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>4330</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>7808</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>9205</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>13395</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1632; 5427</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>5909; 10302</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>1854</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>3925</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>5344</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>5565</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>7199</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>9489</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>15589</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>21114</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>21032</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>21576</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>36622</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>42690</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>12494; 16798</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>19164; 21668</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>17006; 22803</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>18540; 23098</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>32418; 38513</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>38830; 44216</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP16B98-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP16B98-Edad-trans_dic.xlsx
@@ -632,12 +632,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>50,91; 100,0</t>
+          <t>51,34; 100,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>44,17; 100,0</t>
+          <t>44,85; 100,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -652,12 +652,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>72,62; 100,0</t>
+          <t>66,79; 100,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,85; 92,05</t>
+          <t>39,53; 91,85</t>
         </is>
       </c>
     </row>
@@ -712,7 +712,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>35,65; 100,0</t>
+          <t>45,43; 100,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>61,54; 100,0</t>
+          <t>62,46; 100,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>69,19; 100,0</t>
+          <t>68,83; 100,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -802,7 +802,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>30,07; 100,0</t>
+          <t>30,93; 100,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -812,7 +812,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>57,36; 100,0</t>
+          <t>59,46; 100,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -952,12 +952,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>74,38; 100,0</t>
+          <t>77,57; 100,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>88,45; 100,0</t>
+          <t>86,8; 100,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -967,17 +967,17 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>80,27; 100,0</t>
+          <t>80,45; 100,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>81,86; 97,25</t>
+          <t>82,03; 97,47</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>86,74; 98,77</t>
+          <t>86,6; 98,76</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2775; 5450</t>
+          <t>2798; 5450</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1912; 4328</t>
+          <t>1941; 4328</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>7084; 9755</t>
+          <t>6515; 9755</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2454; 6482</t>
+          <t>2784; 6468</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1646; 4618</t>
+          <t>2098; 4618</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4756; 7728</t>
+          <t>4827; 7728</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8543; 12346</t>
+          <t>8497; 12346</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1632; 5427</t>
+          <t>1679; 5427</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5909; 10302</t>
+          <t>6125; 10302</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1654,32 +1654,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>12494; 16798</t>
+          <t>13030; 16798</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>19164; 21668</t>
+          <t>18807; 21668</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>17006; 22803</t>
+          <t>17007; 22803</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>18540; 23098</t>
+          <t>18582; 23098</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>32418; 38513</t>
+          <t>32484; 38602</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>38830; 44216</t>
+          <t>38766; 44211</t>
         </is>
       </c>
     </row>
